--- a/BWI/bestwine_output/bestwine_Chile.xlsx
+++ b/BWI/bestwine_output/bestwine_Chile.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA156"/>
+  <dimension ref="A1:AA157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16821,6 +16821,91 @@
       <c r="Z156" s="2" t="inlineStr"/>
       <c r="AA156" s="2" t="inlineStr"/>
     </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Corcoran Limited, Inc</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Corcoran Limited, Inc</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>82305</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena, Magallanes</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Av. Presidente Carlos Ibáñez Del Campo</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>05765</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://corcoranonline.cl, https://www.corcoran-en.cl</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>contacto@corcoran.cl</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>+56 61 274 0117</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr"/>
+      <c r="R157" s="2" t="inlineStr"/>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/corcoranexpress/</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr"/>
+      <c r="X157" s="2" t="inlineStr"/>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Chile.xlsx
+++ b/BWI/bestwine_output/bestwine_Chile.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16906,6 +16906,91 @@
       <c r="Z157" s="2" t="inlineStr"/>
       <c r="AA157" s="2" t="inlineStr"/>
     </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Corcoran Limited, Inc</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Corcoran Limited, Inc</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>82305</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena, Magallanes</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Av. Presidente Carlos Ibáñez Del Campo</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>05765</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://corcoranonline.cl, https://www.corcoran-en.cl</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>contacto@corcoran.cl</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>+56 61 274 0117</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr"/>
+      <c r="R158" s="2" t="inlineStr"/>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/corcoranexpress/</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr"/>
+      <c r="X158" s="2" t="inlineStr"/>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Chile.xlsx
+++ b/BWI/bestwine_output/bestwine_Chile.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA158"/>
+  <dimension ref="A1:AA160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16991,6 +16991,192 @@
       <c r="Z158" s="2" t="inlineStr"/>
       <c r="AA158" s="2" t="inlineStr"/>
     </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>103737</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>600 Avenida Cañaveral</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pisquera.cl</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>ventas@pisquera.cl</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2668 6500</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>853955000</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr"/>
+      <c r="S159" s="2" t="inlineStr"/>
+      <c r="T159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>Victor Jose</t>
+        </is>
+      </c>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/victorjose-nacharinavon-b2724159</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>103737</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>600 Avenida Cañaveral</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pisquera.cl</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>ventas@pisquera.cl</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2668 6500</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>853955000</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr"/>
+      <c r="S160" s="2" t="inlineStr"/>
+      <c r="T160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
+          <t>Alfredo Planas</t>
+        </is>
+      </c>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>Operations And Logistics Manager</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alfredo-planas-salinas-a7192a46/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Chile.xlsx
+++ b/BWI/bestwine_output/bestwine_Chile.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA160"/>
+  <dimension ref="A1:AA162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17177,6 +17177,192 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>103737</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>600 Avenida Cañaveral</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pisquera.cl</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>ventas@pisquera.cl</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2668 6500</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>853955000</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr"/>
+      <c r="S161" s="2" t="inlineStr"/>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>Victor Jose</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/victorjose-nacharinavon-b2724159</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>103737</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>600 Avenida Cañaveral</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pisquera.cl</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>ventas@pisquera.cl</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2668 6500</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>853955000</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr"/>
+      <c r="S162" s="2" t="inlineStr"/>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr">
+        <is>
+          <t>Alfredo Planas</t>
+        </is>
+      </c>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>Operations And Logistics Manager</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alfredo-planas-salinas-a7192a46/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Chile.xlsx
+++ b/BWI/bestwine_output/bestwine_Chile.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA162"/>
+  <dimension ref="A1:AA164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17363,6 +17363,192 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>103737</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>600 Avenida Cañaveral</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pisquera.cl</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>ventas@pisquera.cl</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2668 6500</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>853955000</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr"/>
+      <c r="S163" s="2" t="inlineStr"/>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr"/>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>Victor Jose</t>
+        </is>
+      </c>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/victorjose-nacharinavon-b2724159</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>103737</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>600 Avenida Cañaveral</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pisquera.cl</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>ventas@pisquera.cl</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2668 6500</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>853955000</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr"/>
+      <c r="S164" s="2" t="inlineStr"/>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr">
+        <is>
+          <t>Alfredo Planas</t>
+        </is>
+      </c>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>Operations And Logistics Manager</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alfredo-planas-salinas-a7192a46/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Chile.xlsx
+++ b/BWI/bestwine_output/bestwine_Chile.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA164"/>
+  <dimension ref="A1:AA166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17549,6 +17549,192 @@
         </is>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>103737</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>600 Avenida Cañaveral</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pisquera.cl</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>ventas@pisquera.cl</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2668 6500</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>853955000</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr"/>
+      <c r="S165" s="2" t="inlineStr"/>
+      <c r="T165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
+          <t>Victor Jose</t>
+        </is>
+      </c>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/victorjose-nacharinavon-b2724159</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>103737</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>600 Avenida Cañaveral</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pisquera.cl</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>ventas@pisquera.cl</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2668 6500</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>853955000</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr"/>
+      <c r="S166" s="2" t="inlineStr"/>
+      <c r="T166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr">
+        <is>
+          <t>Alfredo Planas</t>
+        </is>
+      </c>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>Operations And Logistics Manager</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alfredo-planas-salinas-a7192a46/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Chile.xlsx
+++ b/BWI/bestwine_output/bestwine_Chile.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA166"/>
+  <dimension ref="A1:AA168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17735,6 +17735,192 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>103737</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>600 Avenida Cañaveral</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pisquera.cl</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>ventas@pisquera.cl</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2668 6500</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>853955000</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr"/>
+      <c r="S167" s="2" t="inlineStr"/>
+      <c r="T167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>Victor Jose</t>
+        </is>
+      </c>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/victorjose-nacharinavon-b2724159</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Pisquera Portugal Ltda.</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>103737</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Quilicura</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>600 Avenida Cañaveral</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pisquera.cl</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>ventas@pisquera.cl</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2668 6500</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>853955000</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr"/>
+      <c r="S168" s="2" t="inlineStr"/>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>Alfredo Planas</t>
+        </is>
+      </c>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>Operations And Logistics Manager</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alfredo-planas-salinas-a7192a46/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
